--- a/inputs/data_symbols_TD/04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5.xlsx
+++ b/inputs/data_symbols_TD/04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_TD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E35FC62D-5177-43A7-AE2D-1835827BBE8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9D07969-8A08-43C6-ACB1-2B7DF0BA781B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4155" yWindow="495" windowWidth="18900" windowHeight="11100" xr2:uid="{C93C425D-41FC-4ABC-8EC4-FFB2865443C7}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{B010BB84-EF55-4E6D-938C-9ACA148F0200}"/>
   </bookViews>
   <sheets>
     <sheet name="04_LTAN06_800km_1213COLD_MY_ALL" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7120B849-2843-4673-A611-EB0730796841}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA1A6D2F-EFC1-47A1-BE24-51B016D16AC9}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/inputs/data_symbols_TD/04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5.xlsx
+++ b/inputs/data_symbols_TD/04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9D07969-8A08-43C6-ACB1-2B7DF0BA781B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B8840A2-8C4D-432B-AF03-146EC66DF338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{B010BB84-EF55-4E6D-938C-9ACA148F0200}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{8CA99621-DBCA-4533-B62B-BEA0938F54F5}"/>
   </bookViews>
   <sheets>
     <sheet name="04_LTAN06_800km_1213COLD_MY_ALL" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA1A6D2F-EFC1-47A1-BE24-51B016D16AC9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87411245-28A6-4F87-A52B-B4B38B835622}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>98.977109999999996</v>
+        <v>90.955330000000004</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>98.977109999999996</v>
+        <v>90.955330000000004</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>98.977410000000006</v>
+        <v>90.955309999999997</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
@@ -1073,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>98.97851</v>
+        <v>90.955430000000007</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>98.980710000000002</v>
+        <v>90.9559</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>98.984219999999993</v>
+        <v>90.956879999999998</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>98.989230000000006</v>
+        <v>90.958500000000001</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>98.995900000000006</v>
+        <v>90.960859999999997</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -1143,7 +1143,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>99.004369999999994</v>
+        <v>90.964079999999996</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>99.014780000000002</v>
+        <v>90.968230000000005</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
@@ -1171,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>99.027230000000003</v>
+        <v>90.973389999999995</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>99.041809999999998</v>
+        <v>90.979640000000003</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>99.058599999999998</v>
+        <v>90.987009999999998</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>99.077650000000006</v>
+        <v>90.995549999999994</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
@@ -1227,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>99.098969999999994</v>
+        <v>91.005279999999999</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>99.122559999999993</v>
+        <v>91.016220000000004</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>99.148420000000002</v>
+        <v>91.028369999999995</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
@@ -1269,7 +1269,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>99.176500000000004</v>
+        <v>91.041740000000004</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>99.20675</v>
+        <v>91.056309999999996</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
@@ -1297,7 +1297,7 @@
         <v>3</v>
       </c>
       <c r="D21">
-        <v>99.235320000000002</v>
+        <v>91.070279999999997</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
@@ -1311,7 +1311,7 @@
         <v>3</v>
       </c>
       <c r="D22">
-        <v>99.257750000000001</v>
+        <v>91.081500000000005</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
@@ -1325,7 +1325,7 @@
         <v>3</v>
       </c>
       <c r="D23">
-        <v>99.273120000000006</v>
+        <v>91.089439999999996</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
@@ -1339,7 +1339,7 @@
         <v>3</v>
       </c>
       <c r="D24">
-        <v>99.280690000000007</v>
+        <v>91.093630000000005</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
@@ -1353,7 +1353,7 @@
         <v>3</v>
       </c>
       <c r="D25">
-        <v>99.279809999999998</v>
+        <v>91.093680000000006</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="D26">
-        <v>99.269819999999996</v>
+        <v>91.089160000000007</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
@@ -1381,7 +1381,7 @@
         <v>3</v>
       </c>
       <c r="D27">
-        <v>99.250100000000003</v>
+        <v>91.079689999999999</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
@@ -1395,7 +1395,7 @@
         <v>3</v>
       </c>
       <c r="D28">
-        <v>99.220089999999999</v>
+        <v>91.064880000000002</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
@@ -1409,7 +1409,7 @@
         <v>3</v>
       </c>
       <c r="D29">
-        <v>99.179339999999996</v>
+        <v>91.044439999999994</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
@@ -1423,7 +1423,7 @@
         <v>3</v>
       </c>
       <c r="D30">
-        <v>99.127480000000006</v>
+        <v>91.018109999999993</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
@@ -1437,7 +1437,7 @@
         <v>3</v>
       </c>
       <c r="D31">
-        <v>99.064279999999997</v>
+        <v>90.985680000000002</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
@@ -1451,7 +1451,7 @@
         <v>3</v>
       </c>
       <c r="D32">
-        <v>98.989630000000005</v>
+        <v>90.947019999999995</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
@@ -1465,7 +1465,7 @@
         <v>3</v>
       </c>
       <c r="D33">
-        <v>98.903509999999997</v>
+        <v>90.902079999999998</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
@@ -1479,7 +1479,7 @@
         <v>3</v>
       </c>
       <c r="D34">
-        <v>98.806039999999996</v>
+        <v>90.850840000000005</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.4">
@@ -1493,7 +1493,7 @@
         <v>3</v>
       </c>
       <c r="D35">
-        <v>98.697410000000005</v>
+        <v>90.793340000000001</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.4">
@@ -1507,7 +1507,7 @@
         <v>3</v>
       </c>
       <c r="D36">
-        <v>98.577889999999996</v>
+        <v>90.729680000000002</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.4">
@@ -1521,7 +1521,7 @@
         <v>3</v>
       </c>
       <c r="D37">
-        <v>98.447819999999993</v>
+        <v>90.659980000000004</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.4">
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>98.310689999999994</v>
+        <v>90.586020000000005</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.4">
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>98.170569999999998</v>
+        <v>90.509860000000003</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.4">
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>98.028840000000002</v>
+        <v>90.432220000000001</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.4">
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>97.886740000000003</v>
+        <v>90.353750000000005</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.4">
@@ -1591,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>97.745509999999996</v>
+        <v>90.275099999999995</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.4">
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>97.606340000000003</v>
+        <v>90.196910000000003</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.4">
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>97.470389999999995</v>
+        <v>90.119789999999995</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.4">
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>97.338750000000005</v>
+        <v>90.044349999999994</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.4">
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>97.212400000000002</v>
+        <v>89.971119999999999</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.4">
@@ -1661,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>97.092169999999996</v>
+        <v>89.900599999999997</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.4">
@@ -1675,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>96.978750000000005</v>
+        <v>89.833200000000005</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.4">
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>96.872690000000006</v>
+        <v>89.769229999999993</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.4">
@@ -1703,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>96.774389999999997</v>
+        <v>89.708979999999997</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.4">
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>96.684100000000001</v>
+        <v>89.652619999999999</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.4">
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>96.601979999999998</v>
+        <v>89.600309999999993</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.4">
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>96.52807</v>
+        <v>89.552120000000002</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.4">
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>96.462320000000005</v>
+        <v>89.508089999999996</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.4">
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>96.404640000000001</v>
+        <v>89.468239999999994</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.4">
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>96.354860000000002</v>
+        <v>89.43253</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.4">
@@ -1801,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>96.312780000000004</v>
+        <v>89.400940000000006</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.4">
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>96.278170000000003</v>
+        <v>89.373400000000004</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.4">
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>96.250780000000006</v>
+        <v>89.349850000000004</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.4">
@@ -1843,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>96.230320000000006</v>
+        <v>89.330200000000005</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.4">
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>96.216489999999993</v>
+        <v>89.314359999999994</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.4">
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>96.20899</v>
+        <v>89.302210000000002</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.4">
@@ -1885,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>96.207490000000007</v>
+        <v>89.293629999999993</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.4">
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>96.211680000000001</v>
+        <v>89.288480000000007</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.4">
@@ -1913,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>96.221230000000006</v>
+        <v>89.286640000000006</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.4">
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>96.235830000000007</v>
+        <v>89.287949999999995</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.4">
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>96.255139999999997</v>
+        <v>89.292259999999999</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.4">
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>96.278840000000002</v>
+        <v>89.299419999999998</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.4">
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>96.306629999999998</v>
+        <v>89.309269999999998</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.4">
@@ -1983,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>96.338189999999997</v>
+        <v>89.321659999999994</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.4">
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>96.373220000000003</v>
+        <v>89.336439999999996</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.4">
@@ -2011,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>96.411460000000005</v>
+        <v>89.353430000000003</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.4">
@@ -2025,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>96.452619999999996</v>
+        <v>89.372489999999999</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.4">
@@ -2039,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>96.496459999999999</v>
+        <v>89.393450000000001</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.4">
@@ -2053,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>96.54271</v>
+        <v>89.416139999999999</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.4">
@@ -2067,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>96.591120000000004</v>
+        <v>89.440399999999997</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.4">
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>96.641450000000006</v>
+        <v>89.466089999999994</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.4">
@@ -2095,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>96.693470000000005</v>
+        <v>89.493080000000006</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.4">
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>96.746970000000005</v>
+        <v>89.52122</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.4">
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>96.801779999999994</v>
+        <v>89.550389999999993</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.4">
@@ -2137,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>96.857699999999994</v>
+        <v>89.580449999999999</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.4">
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>96.914569999999998</v>
+        <v>89.6113</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.4">
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>96.972229999999996</v>
+        <v>89.642790000000005</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.4">
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>97.030540000000002</v>
+        <v>89.674840000000003</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.4">
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>97.089370000000002</v>
+        <v>89.707340000000002</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.4">
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>97.148589999999999</v>
+        <v>89.740200000000002</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.4">
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>97.208089999999999</v>
+        <v>89.773340000000005</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.4">
@@ -2235,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>97.267790000000005</v>
+        <v>89.806690000000003</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.4">
@@ -2249,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>97.327579999999998</v>
+        <v>89.840180000000004</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.4">
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>97.387420000000006</v>
+        <v>89.873750000000001</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.4">
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>97.447230000000005</v>
+        <v>89.907340000000005</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.4">
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>97.506979999999999</v>
+        <v>89.940929999999994</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.4">
@@ -2305,7 +2305,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>97.566609999999997</v>
+        <v>89.974469999999997</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.4">
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>97.626109999999997</v>
+        <v>90.007930000000002</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.4">
@@ -2333,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>97.685429999999997</v>
+        <v>90.04128</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.4">
@@ -2347,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>97.744569999999996</v>
+        <v>90.0745</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.4">
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>97.803510000000003</v>
+        <v>90.107590000000002</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.4">
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>97.862260000000006</v>
+        <v>90.140529999999998</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.4">
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>97.920810000000003</v>
+        <v>90.173330000000007</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.4">
@@ -2403,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>97.979179999999999</v>
+        <v>90.206000000000003</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.4">
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>98.037360000000007</v>
+        <v>90.238529999999997</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.4">
@@ -2431,7 +2431,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>98.095399999999998</v>
+        <v>90.270960000000002</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.4">
@@ -2445,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>98.153319999999994</v>
+        <v>90.303309999999996</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.4">
@@ -2459,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>98.211150000000004</v>
+        <v>90.335610000000003</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.4">
@@ -2473,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>98.268910000000005</v>
+        <v>90.36788</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.4">
@@ -2487,7 +2487,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>98.326639999999998</v>
+        <v>90.400149999999996</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.4">
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>98.384349999999998</v>
+        <v>90.432429999999997</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.4">
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>98.442070000000001</v>
+        <v>90.464759999999998</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.4">
@@ -2529,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>98.499830000000003</v>
+        <v>90.497140000000002</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.4">
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>98.557649999999995</v>
+        <v>90.529589999999999</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.4">
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>98.615530000000007</v>
+        <v>90.562129999999996</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.4">
@@ -2571,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>98.673509999999993</v>
+        <v>90.59478</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.4">
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>98.731610000000003</v>
+        <v>90.627529999999993</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.4">
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>98.789860000000004</v>
+        <v>90.660420000000002</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.4">
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>98.848259999999996</v>
+        <v>90.693449999999999</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.4">
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>98.906850000000006</v>
+        <v>90.726609999999994</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.4">
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>98.965630000000004</v>
+        <v>90.759929999999997</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.4">
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>99.024609999999996</v>
+        <v>90.793409999999994</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.4">
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="D119">
-        <v>99.083820000000003</v>
+        <v>90.827060000000003</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.4">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>99.143240000000006</v>
+        <v>90.860889999999998</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.4">
@@ -2697,7 +2697,7 @@
         <v>3</v>
       </c>
       <c r="D121">
-        <v>99.199060000000003</v>
+        <v>90.893100000000004</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.4">
@@ -2711,7 +2711,7 @@
         <v>3</v>
       </c>
       <c r="D122">
-        <v>99.246840000000006</v>
+        <v>90.921549999999996</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.4">
@@ -2725,7 +2725,7 @@
         <v>3</v>
       </c>
       <c r="D123">
-        <v>99.285740000000004</v>
+        <v>90.945740000000001</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.4">
@@ -2739,7 +2739,7 @@
         <v>3</v>
       </c>
       <c r="D124">
-        <v>99.315129999999996</v>
+        <v>90.965249999999997</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.4">
@@ -2753,7 +2753,7 @@
         <v>3</v>
       </c>
       <c r="D125">
-        <v>99.334419999999994</v>
+        <v>90.979709999999997</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.4">
@@ -2767,7 +2767,7 @@
         <v>3</v>
       </c>
       <c r="D126">
-        <v>99.343050000000005</v>
+        <v>90.988730000000004</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.4">
@@ -2781,7 +2781,7 @@
         <v>3</v>
       </c>
       <c r="D127">
-        <v>99.340500000000006</v>
+        <v>90.991969999999995</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.4">
@@ -2795,7 +2795,7 @@
         <v>3</v>
       </c>
       <c r="D128">
-        <v>99.326300000000003</v>
+        <v>90.989099999999993</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.4">
@@ -2809,7 +2809,7 @@
         <v>3</v>
       </c>
       <c r="D129">
-        <v>99.300060000000002</v>
+        <v>90.979839999999996</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.4">
@@ -2823,7 +2823,7 @@
         <v>3</v>
       </c>
       <c r="D130">
-        <v>99.261520000000004</v>
+        <v>90.963970000000003</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.4">
@@ -2837,7 +2837,7 @@
         <v>3</v>
       </c>
       <c r="D131">
-        <v>99.210539999999995</v>
+        <v>90.941339999999997</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.4">
@@ -2851,7 +2851,7 @@
         <v>3</v>
       </c>
       <c r="D132">
-        <v>99.147059999999996</v>
+        <v>90.911850000000001</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.4">
@@ -2865,7 +2865,7 @@
         <v>3</v>
       </c>
       <c r="D133">
-        <v>99.071160000000006</v>
+        <v>90.875479999999996</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.4">
@@ -2879,7 +2879,7 @@
         <v>3</v>
       </c>
       <c r="D134">
-        <v>98.983009999999993</v>
+        <v>90.832239999999999</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.4">
@@ -2893,7 +2893,7 @@
         <v>3</v>
       </c>
       <c r="D135">
-        <v>98.88288</v>
+        <v>90.782219999999995</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.4">
@@ -2907,7 +2907,7 @@
         <v>3</v>
       </c>
       <c r="D136">
-        <v>98.771090000000001</v>
+        <v>90.725530000000006</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.4">
@@ -2921,7 +2921,7 @@
         <v>3</v>
       </c>
       <c r="D137">
-        <v>98.648049999999998</v>
+        <v>90.66234</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.4">
@@ -2935,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="D138">
-        <v>98.517300000000006</v>
+        <v>90.594459999999998</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.4">
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="D139">
-        <v>98.383009999999999</v>
+        <v>90.523970000000006</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.4">
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="D140">
-        <v>98.246560000000002</v>
+        <v>90.451629999999994</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.4">
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="D141">
-        <v>98.109279999999998</v>
+        <v>90.378110000000007</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.4">
@@ -2991,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="D142">
-        <v>97.972409999999996</v>
+        <v>90.304079999999999</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.4">
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="D143">
-        <v>97.837190000000007</v>
+        <v>90.230189999999993</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.4">
@@ -3019,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="D144">
-        <v>97.704830000000001</v>
+        <v>90.1571</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.4">
@@ -3033,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="D145">
-        <v>97.576419999999999</v>
+        <v>90.085409999999996</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.4">
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="D146">
-        <v>97.452969999999993</v>
+        <v>90.015690000000006</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.4">
@@ -3061,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="D147">
-        <v>97.335350000000005</v>
+        <v>89.948430000000002</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.4">
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="D148">
-        <v>97.224270000000004</v>
+        <v>89.884060000000005</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.4">
@@ -3089,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="D149">
-        <v>97.120279999999994</v>
+        <v>89.822929999999999</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.4">
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="D150">
-        <v>97.023809999999997</v>
+        <v>89.765309999999999</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.4">
@@ -3117,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="D151">
-        <v>96.935130000000001</v>
+        <v>89.711399999999998</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.4">
@@ -3131,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="D152">
-        <v>96.854410000000001</v>
+        <v>89.661360000000002</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.4">
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="D153">
-        <v>96.781700000000001</v>
+        <v>89.615279999999998</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.4">
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="D154">
-        <v>96.716980000000007</v>
+        <v>89.573220000000006</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.4">
@@ -3173,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="D155">
-        <v>96.660160000000005</v>
+        <v>89.535179999999997</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.4">
@@ -3187,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="D156">
-        <v>96.611080000000001</v>
+        <v>89.501159999999999</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.4">
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="D157">
-        <v>96.569559999999996</v>
+        <v>89.471119999999999</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.4">
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="D158">
-        <v>96.53537</v>
+        <v>89.44502</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.4">
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="D159">
-        <v>96.508269999999996</v>
+        <v>89.422799999999995</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.4">
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="D160">
-        <v>96.487979999999993</v>
+        <v>89.40437</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.4">
@@ -3257,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="D161">
-        <v>96.474220000000003</v>
+        <v>89.38964</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.4">
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="D162">
-        <v>96.466669999999993</v>
+        <v>89.378519999999995</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.4">
@@ -3285,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="D163">
-        <v>96.465040000000002</v>
+        <v>89.37088</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.4">
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="D164">
-        <v>96.469009999999997</v>
+        <v>89.366600000000005</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.4">
@@ -3313,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="D165">
-        <v>96.478250000000003</v>
+        <v>89.365539999999996</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.4">
@@ -3327,7 +3327,7 @@
         <v>0</v>
       </c>
       <c r="D166">
-        <v>96.492459999999994</v>
+        <v>89.367559999999997</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.4">
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="D167">
-        <v>96.511309999999995</v>
+        <v>89.372519999999994</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.4">
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="D168">
-        <v>96.534499999999994</v>
+        <v>89.380260000000007</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.4">
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="D169">
-        <v>96.561710000000005</v>
+        <v>89.390640000000005</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.4">
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="D170">
-        <v>96.59263</v>
+        <v>89.403499999999994</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.4">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="D171">
-        <v>96.62697</v>
+        <v>89.418689999999998</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.4">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="D172">
-        <v>96.664469999999994</v>
+        <v>89.436049999999994</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.4">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="D173">
-        <v>96.704859999999996</v>
+        <v>89.455430000000007</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.4">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="D174">
-        <v>96.747879999999995</v>
+        <v>89.476669999999999</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.4">
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="D175">
-        <v>96.793270000000007</v>
+        <v>89.499600000000001</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.4">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="D176">
-        <v>96.840789999999998</v>
+        <v>89.524060000000006</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.4">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="D177">
-        <v>96.890199999999993</v>
+        <v>89.549930000000003</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.4">
@@ -3495,7 +3495,7 @@
         <v>0</v>
       </c>
       <c r="D178">
-        <v>96.941270000000003</v>
+        <v>89.577039999999997</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.4">
@@ -3509,7 +3509,7 @@
         <v>0</v>
       </c>
       <c r="D179">
-        <v>96.993799999999993</v>
+        <v>89.605289999999997</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.4">
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="D180">
-        <v>97.047600000000003</v>
+        <v>89.634529999999998</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.4">
@@ -3537,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="D181">
-        <v>97.102500000000006</v>
+        <v>89.664649999999995</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.4">
@@ -3551,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="D182">
-        <v>97.158339999999995</v>
+        <v>89.695520000000002</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.4">
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="D183">
-        <v>97.214939999999999</v>
+        <v>89.727019999999996</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.4">
@@ -3579,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="D184">
-        <v>97.272189999999995</v>
+        <v>89.759039999999999</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.4">
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="D185">
-        <v>97.329930000000004</v>
+        <v>89.791499999999999</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.4">
@@ -3607,7 +3607,7 @@
         <v>0</v>
       </c>
       <c r="D186">
-        <v>97.388050000000007</v>
+        <v>89.824299999999994</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.4">
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="D187">
-        <v>97.446449999999999</v>
+        <v>89.857370000000003</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.4">
@@ -3635,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="D188">
-        <v>97.505030000000005</v>
+        <v>89.890619999999998</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.4">
@@ -3649,7 +3649,7 @@
         <v>0</v>
       </c>
       <c r="D189">
-        <v>97.56371</v>
+        <v>89.924000000000007</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.4">
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="D190">
-        <v>97.622410000000002</v>
+        <v>89.957449999999994</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.4">
@@ -3677,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="D191">
-        <v>97.681089999999998</v>
+        <v>89.99091</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.4">
@@ -3691,7 +3691,7 @@
         <v>0</v>
       </c>
       <c r="D192">
-        <v>97.739699999999999</v>
+        <v>90.024349999999998</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.4">
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="D193">
-        <v>97.798190000000005</v>
+        <v>90.057730000000006</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.4">
@@ -3719,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="D194">
-        <v>97.856539999999995</v>
+        <v>90.09102</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.4">
@@ -3733,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="D195">
-        <v>97.914709999999999</v>
+        <v>90.124189999999999</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.4">
@@ -3747,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="D196">
-        <v>97.972700000000003</v>
+        <v>90.157229999999998</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.4">
@@ -3761,7 +3761,7 @@
         <v>0</v>
       </c>
       <c r="D197">
-        <v>98.030500000000004</v>
+        <v>90.190119999999993</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.4">
@@ -3775,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="D198">
-        <v>98.088089999999994</v>
+        <v>90.222859999999997</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.4">
@@ -3789,7 +3789,7 @@
         <v>0</v>
       </c>
       <c r="D199">
-        <v>98.145489999999995</v>
+        <v>90.255449999999996</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.4">
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="D200">
-        <v>98.202709999999996</v>
+        <v>90.287890000000004</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.4">
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="D201">
-        <v>98.259749999999997</v>
+        <v>90.3202</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.4">
@@ -3831,7 +3831,7 @@
         <v>0</v>
       </c>
       <c r="D202">
-        <v>98.316640000000007</v>
+        <v>90.352400000000003</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.4">
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="D203">
-        <v>98.373419999999996</v>
+        <v>90.384519999999995</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.4">
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="D204">
-        <v>98.430099999999996</v>
+        <v>90.416579999999996</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.4">
@@ -3873,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="D205">
-        <v>98.486720000000005</v>
+        <v>90.448610000000002</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.4">
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="D206">
-        <v>98.543310000000005</v>
+        <v>90.480630000000005</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.4">
@@ -3901,7 +3901,7 @@
         <v>0</v>
       </c>
       <c r="D207">
-        <v>98.599890000000002</v>
+        <v>90.512659999999997</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.4">
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="D208">
-        <v>98.656490000000005</v>
+        <v>90.544730000000001</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.4">
@@ -3929,7 +3929,7 @@
         <v>0</v>
       </c>
       <c r="D209">
-        <v>98.713120000000004</v>
+        <v>90.576859999999996</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.4">
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="D210">
-        <v>98.769810000000007</v>
+        <v>90.609049999999996</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.4">
@@ -3957,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="D211">
-        <v>98.826580000000007</v>
+        <v>90.641329999999996</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.4">
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="D212">
-        <v>98.883449999999996</v>
+        <v>90.67371</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.4">
@@ -3985,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="D213">
-        <v>98.940439999999995</v>
+        <v>90.706199999999995</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.4">
@@ -3999,7 +3999,7 @@
         <v>0</v>
       </c>
       <c r="D214">
-        <v>98.997579999999999</v>
+        <v>90.738820000000004</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.4">
@@ -4013,7 +4013,7 @@
         <v>0</v>
       </c>
       <c r="D215">
-        <v>99.054879999999997</v>
+        <v>90.771569999999997</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.4">
@@ -4027,7 +4027,7 @@
         <v>0</v>
       </c>
       <c r="D216">
-        <v>99.112369999999999</v>
+        <v>90.804469999999995</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.4">
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="D217">
-        <v>99.170060000000007</v>
+        <v>90.837519999999998</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.4">
@@ -4055,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="D218">
-        <v>99.227959999999996</v>
+        <v>90.870729999999995</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.4">
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="D219">
-        <v>99.286090000000002</v>
+        <v>90.9041</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.4">
@@ -4083,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="D220">
-        <v>99.344440000000006</v>
+        <v>90.937659999999994</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.4">
@@ -4097,7 +4097,7 @@
         <v>3</v>
       </c>
       <c r="D221">
-        <v>99.399180000000001</v>
+        <v>90.969589999999997</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.4">
@@ -4111,7 +4111,7 @@
         <v>3</v>
       </c>
       <c r="D222">
-        <v>99.445880000000002</v>
+        <v>90.99776</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.4">
@@ -4125,7 +4125,7 @@
         <v>3</v>
       </c>
       <c r="D223">
-        <v>99.483699999999999</v>
+        <v>91.02167</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.4">
@@ -4139,7 +4139,7 @@
         <v>3</v>
       </c>
       <c r="D224">
-        <v>99.512</v>
+        <v>91.040890000000005</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.4">
@@ -4153,7 +4153,7 @@
         <v>3</v>
       </c>
       <c r="D225">
-        <v>99.530199999999994</v>
+        <v>91.055059999999997</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.4">
@@ -4167,7 +4167,7 @@
         <v>3</v>
       </c>
       <c r="D226">
-        <v>99.537750000000003</v>
+        <v>91.063800000000001</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.4">
@@ -4181,7 +4181,7 @@
         <v>3</v>
       </c>
       <c r="D227">
-        <v>99.534099999999995</v>
+        <v>91.066739999999996</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.4">
@@ -4195,7 +4195,7 @@
         <v>3</v>
       </c>
       <c r="D228">
-        <v>99.518799999999999</v>
+        <v>91.063580000000002</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.4">
@@ -4209,7 +4209,7 @@
         <v>3</v>
       </c>
       <c r="D229">
-        <v>99.491470000000007</v>
+        <v>91.054019999999994</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.4">
@@ -4223,7 +4223,7 @@
         <v>3</v>
       </c>
       <c r="D230">
-        <v>99.451840000000004</v>
+        <v>91.037850000000006</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.4">
@@ -4237,7 +4237,7 @@
         <v>3</v>
       </c>
       <c r="D231">
-        <v>99.399760000000001</v>
+        <v>91.014930000000007</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.4">
@@ -4251,7 +4251,7 @@
         <v>3</v>
       </c>
       <c r="D232">
-        <v>99.335189999999997</v>
+        <v>90.985140000000001</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.4">
@@ -4265,7 +4265,7 @@
         <v>3</v>
       </c>
       <c r="D233">
-        <v>99.258200000000002</v>
+        <v>90.948459999999997</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.4">
@@ -4279,7 +4279,7 @@
         <v>3</v>
       </c>
       <c r="D234">
-        <v>99.168970000000002</v>
+        <v>90.904920000000004</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.4">
@@ -4293,7 +4293,7 @@
         <v>3</v>
       </c>
       <c r="D235">
-        <v>99.067750000000004</v>
+        <v>90.854600000000005</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.4">
@@ -4307,7 +4307,7 @@
         <v>3</v>
       </c>
       <c r="D236">
-        <v>98.954899999999995</v>
+        <v>90.797619999999995</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.4">
@@ -4321,7 +4321,7 @@
         <v>3</v>
       </c>
       <c r="D237">
-        <v>98.830780000000004</v>
+        <v>90.734129999999993</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.4">
@@ -4335,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="D238">
-        <v>98.698989999999995</v>
+        <v>90.665949999999995</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.4">
@@ -4349,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="D239">
-        <v>98.563649999999996</v>
+        <v>90.595160000000007</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.4">
@@ -4363,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="D240">
-        <v>98.426190000000005</v>
+        <v>90.522530000000003</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.4">
@@ -4377,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="D241">
-        <v>98.287899999999993</v>
+        <v>90.448719999999994</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.4">
@@ -4391,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="D242">
-        <v>98.150040000000004</v>
+        <v>90.374399999999994</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.4">
@@ -4405,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="D243">
-        <v>98.013859999999994</v>
+        <v>90.300229999999999</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.4">
@@ -4419,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="D244">
-        <v>97.880539999999996</v>
+        <v>90.226860000000002</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.4">
@@ -4433,7 +4433,7 @@
         <v>0</v>
       </c>
       <c r="D245">
-        <v>97.751199999999997</v>
+        <v>90.154899999999998</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.4">
@@ -4447,7 +4447,7 @@
         <v>0</v>
       </c>
       <c r="D246">
-        <v>97.626829999999998</v>
+        <v>90.084900000000005</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.4">
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="D247">
-        <v>97.508309999999994</v>
+        <v>90.01737</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.4">
@@ -4475,7 +4475,7 @@
         <v>0</v>
       </c>
       <c r="D248">
-        <v>97.396339999999995</v>
+        <v>89.952740000000006</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.4">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="D249">
-        <v>97.291470000000004</v>
+        <v>89.891350000000003</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.4">
@@ -4503,7 +4503,7 @@
         <v>0</v>
       </c>
       <c r="D250">
-        <v>97.194140000000004</v>
+        <v>89.833470000000005</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.4">
@@ -4517,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="D251">
-        <v>97.104609999999994</v>
+        <v>89.779300000000006</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.4">
@@ -4531,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="D252">
-        <v>97.023049999999998</v>
+        <v>89.729010000000002</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.4">
@@ -4545,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="D253">
-        <v>96.949510000000004</v>
+        <v>89.682680000000005</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.4">
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="D254">
-        <v>96.883970000000005</v>
+        <v>89.640360000000001</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.4">
@@ -4573,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="D255">
-        <v>96.826340000000002</v>
+        <v>89.602080000000001</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.4">
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="D256">
-        <v>96.776449999999997</v>
+        <v>89.567809999999994</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.4">
@@ -4601,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="D257">
-        <v>96.734129999999993</v>
+        <v>89.537530000000004</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.4">
@@ -4615,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="D258">
-        <v>96.69914</v>
+        <v>89.511189999999999</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.4">
@@ -4629,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="D259">
-        <v>96.671250000000001</v>
+        <v>89.488720000000001</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.4">
@@ -4643,7 +4643,7 @@
         <v>0</v>
       </c>
       <c r="D260">
-        <v>96.650180000000006</v>
+        <v>89.470050000000001</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.4">
@@ -4657,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="D261">
-        <v>96.635630000000006</v>
+        <v>89.455089999999998</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.4">
@@ -4671,7 +4671,7 @@
         <v>0</v>
       </c>
       <c r="D262">
-        <v>96.627309999999994</v>
+        <v>89.443730000000002</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.4">
@@ -4685,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="D263">
-        <v>96.624899999999997</v>
+        <v>89.435860000000005</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.4">
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="D264">
-        <v>96.628100000000003</v>
+        <v>89.431340000000006</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.4">
@@ -4713,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="D265">
-        <v>96.636579999999995</v>
+        <v>89.430049999999994</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.4">
@@ -4727,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="D266">
-        <v>96.650019999999998</v>
+        <v>89.431830000000005</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.4">
@@ -4741,7 +4741,7 @@
         <v>0</v>
       </c>
       <c r="D267">
-        <v>96.668109999999999</v>
+        <v>89.43656</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.4">
@@ -4755,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="D268">
-        <v>96.690539999999999</v>
+        <v>89.444059999999993</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.4">
@@ -4769,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="D269">
-        <v>96.716980000000007</v>
+        <v>89.454210000000003</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.4">
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="D270">
-        <v>96.747140000000002</v>
+        <v>89.466840000000005</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.4">
@@ -4797,7 +4797,7 @@
         <v>0</v>
       </c>
       <c r="D271">
-        <v>96.780730000000005</v>
+        <v>89.481800000000007</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.4">
@@ -4811,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="D272">
-        <v>96.817480000000003</v>
+        <v>89.498930000000001</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.4">
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="D273">
-        <v>96.857110000000006</v>
+        <v>89.518079999999998</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.4">
@@ -4839,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="D274">
-        <v>96.899379999999994</v>
+        <v>89.539090000000002</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.4">
@@ -4853,7 +4853,7 @@
         <v>0</v>
       </c>
       <c r="D275">
-        <v>96.944019999999995</v>
+        <v>89.561779999999999</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.4">
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="D276">
-        <v>96.990790000000004</v>
+        <v>89.586020000000005</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.4">
@@ -4881,7 +4881,7 @@
         <v>0</v>
       </c>
       <c r="D277">
-        <v>97.039450000000002</v>
+        <v>89.611649999999997</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.4">
@@ -4895,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="D278">
-        <v>97.089780000000005</v>
+        <v>89.638540000000006</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.4">
@@ -4909,7 +4909,7 @@
         <v>0</v>
       </c>
       <c r="D279">
-        <v>97.141559999999998</v>
+        <v>89.666560000000004</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.4">
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="D280">
-        <v>97.194630000000004</v>
+        <v>89.695580000000007</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.4">
@@ -4937,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="D281">
-        <v>97.24879</v>
+        <v>89.725459999999998</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.4">
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="D282">
-        <v>97.303889999999996</v>
+        <v>89.756110000000007</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.4">
@@ -4965,7 +4965,7 @@
         <v>0</v>
       </c>
       <c r="D283">
-        <v>97.359759999999994</v>
+        <v>89.787379999999999</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.4">
@@ -4979,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="D284">
-        <v>97.416269999999997</v>
+        <v>89.819180000000003</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.4">
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="D285">
-        <v>97.473280000000003</v>
+        <v>89.851410000000001</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.4">
@@ -5007,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="D286">
-        <v>97.530670000000001</v>
+        <v>89.883979999999994</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.4">
@@ -5021,7 +5021,7 @@
         <v>0</v>
       </c>
       <c r="D287">
-        <v>97.588340000000002</v>
+        <v>89.916830000000004</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.4">
@@ -5035,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="D288">
-        <v>97.646199999999993</v>
+        <v>89.949860000000001</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.4">
@@ -5049,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="D289">
-        <v>97.704149999999998</v>
+        <v>89.983009999999993</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.4">
@@ -5063,7 +5063,7 @@
         <v>0</v>
       </c>
       <c r="D290">
-        <v>97.762129999999999</v>
+        <v>90.016229999999993</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.4">
@@ -5077,7 +5077,7 @@
         <v>0</v>
       </c>
       <c r="D291">
-        <v>97.820089999999993</v>
+        <v>90.049469999999999</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.4">
@@ -5091,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="D292">
-        <v>97.877979999999994</v>
+        <v>90.082689999999999</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.4">
@@ -5105,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="D293">
-        <v>97.935770000000005</v>
+        <v>90.115849999999995</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.4">
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="D294">
-        <v>97.993399999999994</v>
+        <v>90.148920000000004</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.4">
@@ -5133,7 +5133,7 @@
         <v>0</v>
       </c>
       <c r="D295">
-        <v>98.050870000000003</v>
+        <v>90.181870000000004</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.4">
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="D296">
-        <v>98.108149999999995</v>
+        <v>90.214680000000001</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.4">
@@ -5161,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="D297">
-        <v>98.165239999999997</v>
+        <v>90.247349999999997</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.4">
@@ -5175,7 +5175,7 @@
         <v>0</v>
       </c>
       <c r="D298">
-        <v>98.222139999999996</v>
+        <v>90.279870000000003</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.4">
@@ -5189,7 +5189,7 @@
         <v>0</v>
       </c>
       <c r="D299">
-        <v>98.278840000000002</v>
+        <v>90.312240000000003</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.4">
@@ -5203,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="D300">
-        <v>98.335359999999994</v>
+        <v>90.344470000000001</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.4">
@@ -5217,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="D301">
-        <v>98.391710000000003</v>
+        <v>90.376559999999998</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.4">
@@ -5231,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="D302">
-        <v>98.447919999999996</v>
+        <v>90.408540000000002</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.4">
@@ -5245,7 +5245,7 @@
         <v>0</v>
       </c>
       <c r="D303">
-        <v>98.504009999999994</v>
+        <v>90.440439999999995</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/data_symbols_TD/04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5.xlsx
+++ b/inputs/data_symbols_TD/04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B8840A2-8C4D-432B-AF03-146EC66DF338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AAADCB87-B6E6-4380-AB28-6EEE68A2B6DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{8CA99621-DBCA-4533-B62B-BEA0938F54F5}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{0243304F-05BC-4D36-ABBB-F897D2923A53}"/>
   </bookViews>
   <sheets>
     <sheet name="04_LTAN06_800km_1213COLD_MY_ALL" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87411245-28A6-4F87-A52B-B4B38B835622}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23AD57F3-6E80-4E0D-94AC-15409B0D7434}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/inputs/data_symbols_TD/04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5.xlsx
+++ b/inputs/data_symbols_TD/04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AAADCB87-B6E6-4380-AB28-6EEE68A2B6DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D3F3F12-6EE5-4782-BED7-FAD1B5647714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{0243304F-05BC-4D36-ABBB-F897D2923A53}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{3DAAD705-6A7F-4099-A283-2D3598984BD9}"/>
   </bookViews>
   <sheets>
     <sheet name="04_LTAN06_800km_1213COLD_MY_ALL" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23AD57F3-6E80-4E0D-94AC-15409B0D7434}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BD9F06B-38F9-465F-A4A4-44AF7AC7FEED}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
